--- a/klasemen 25_26/klasemen premier_league.xlsx
+++ b/klasemen 25_26/klasemen premier_league.xlsx
@@ -434,6 +434,9 @@
       <c r="J1" t="str">
         <v>Poin</v>
       </c>
+      <c r="K1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -466,6 +469,9 @@
       <c r="J2">
         <v>85</v>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -638,6 +644,9 @@
       <c r="J7">
         <v>57</v>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -705,6 +714,9 @@
       <c r="J9">
         <v>53</v>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -947,6 +959,9 @@
       <c r="J16">
         <v>45</v>
       </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1049,6 +1064,9 @@
       <c r="J19">
         <v>39</v>
       </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1090,7 +1108,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Wolverhampton Wanderers (R)</v>
+        <v>Wolverhampton Wanderers</v>
       </c>
       <c r="C21">
         <v>38</v>
